--- a/mortgage_reviewed.xlsx
+++ b/mortgage_reviewed.xlsx
@@ -59,14 +59,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00DDEBF7"/>
+        <bgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DDEBF7"/>
-        <bgColor rgb="00DDEBF7"/>
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -95,8 +95,8 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -466,12 +466,12 @@
   <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="62" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -546,147 +546,155 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
+          <t>Jennifer Houston</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>SVP</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>jhouston@cmgfi.com</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>senior exec in corridor</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>CMG Home Loans</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
           <t>Phil George</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>Marketing Director</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>pgeorge@cmgfi.com</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>top marketing at this company</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>top marketing</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>CMG Home Loans</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>John Weaver</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>Marketing Manager</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>jweaver@cmgfi.com</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>marketing</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>CMG Home Loans</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Michele Sniffen</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Processing Manager</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>msniffen@cmgfi.com</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>RED</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>back office - not exec/VP/director or marketing</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>CMG Home Loans</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Jennifer Ho***n</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>SVP</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr"/>
-      <c r="E6" s="4" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>DHI Mortgage Co. Ltd.</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Sonya Luechauer</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>President and Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>sluechauer@dhimortgage.com</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>ADD</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>senior exec in corridor</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>DHI Mortgage Co. Ltd.</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Monica Ka***r</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>AVP, National Marketing Manager</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr"/>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>highest marketing at DHI</t>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>C-level, in corridor</t>
         </is>
       </c>
     </row>
@@ -698,59 +706,59 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
+          <t>Monica Kaspar</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>AVP, National Marketing Manager</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>makaspar@dhimortgage.com</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>highest marketing at DHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>DHI Mortgage Co. Ltd.</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
           <t>Thomas VanBuskirk</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>Digital Marketing Manager</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>tvanbuskirk@dhimortgage.com</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>marketing - NOTE your sheet lists him as branch sales manager, Apollo says Digital Marketing Manager</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>DHI Mortgage Co. Ltd.</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Viky Kalyta</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Marketing Coordinator</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>vkalyta@dhimortgage.com</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>KEEP</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>marketing, lowest rank of the three</t>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>marketing - your sheet says branch sales manager, Apollo says Digital Marketing Manager</t>
         </is>
       </c>
     </row>
@@ -762,23 +770,27 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Sonya Lu***r</t>
+          <t>Viky Kalyta</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>President and Chief Executive Officer</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr"/>
+          <t>Marketing Coordinator</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>vkalyta@dhimortgage.com</t>
+        </is>
+      </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>ADD</t>
+          <t>KEEP</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>C-level, in corridor</t>
+          <t>marketing, lowest of the three</t>
         </is>
       </c>
     </row>
@@ -822,27 +834,27 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Andrew Brock</t>
+          <t>Greg Schaub</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>South region head, private bank</t>
+          <t>EVP Sales</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>andrew.j.brock@jpmorgan.com</t>
+          <t>greg.schaub@chase.com</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>KEEP</t>
+          <t>ADD</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>regional head</t>
+          <t>EVP in corridor</t>
         </is>
       </c>
     </row>
@@ -854,23 +866,27 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Greg Sc***b</t>
+          <t>Andrew Brock</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>EVP Sales</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr"/>
+          <t>South region head, private bank</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>andrew.j.brock@jpmorgan.com</t>
+        </is>
+      </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>ADD</t>
+          <t>KEEP</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>EVP in corridor</t>
+          <t>regional head</t>
         </is>
       </c>
     </row>
@@ -971,32 +987,32 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Lennar Mortgage</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Kyle Simpson</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>SVP, Regional Manager</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>KyleSimpson@lennarmortgage.com</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>SVP - your sheet had no title, Apollo confirms</t>
         </is>
@@ -1067,58 +1083,66 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>Fairway Independent Mortgage</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>Chandler Ha***n</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Matt Wood</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Managing Partner</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>mwood@fairwaymc.com</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>exec in corridor</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Fairway Independent Mortgage</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Chandler Hansen</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>Marketing Manager</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr"/>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>chandler.hansen@fairwaymc.com</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>ADD</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>top marketing in corridor</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>Fairway Independent Mortgage</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Matt Wo***d</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Managing Partner</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr"/>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>exec in corridor</t>
         </is>
       </c>
     </row>
@@ -1182,7 +1206,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>loan officer - not exec/VP/director or marketing</t>
+          <t>loan officer</t>
         </is>
       </c>
     </row>
@@ -1283,122 +1307,130 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>LoanPeople</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>Max Leaman</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>CEO</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>max.leaman@loanpeople.com</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>C-level</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>LoanPeople</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>Dana Leaman</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>CMO</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>Dana@maxleaman.com</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="E28" s="4" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
-      <c r="F28" s="3" t="inlineStr">
+      <c r="F28" s="4" t="inlineStr">
         <is>
           <t>top marketing - CMO</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>Pulte Mortgage LLC</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Stephanie Re***g</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Pablo Rivas</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Division President</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>pablo.rivas@pultegroup.com</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>president</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Pulte Mortgage LLC</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Stephanie Redding</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>Director of Marketing</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr"/>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>stephanie.redding@pultegroup.com</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>ADD</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr">
+      <c r="F30" s="3" t="inlineStr">
         <is>
           <t>top marketing in corridor</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>Pulte Mortgage LLC</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>Pablo Rivas</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>Division president</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr"/>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>president - needs email, Apollo has him</t>
         </is>
       </c>
     </row>
@@ -1431,30 +1463,34 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>KBHS Home Loans LLC</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>Louie Colatriano</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr"/>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>lcolatriano1@kbhshomeloans.com</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t>ADD</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>president - needs email</t>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>president</t>
         </is>
       </c>
     </row>
@@ -1519,28 +1555,32 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>M/I Financial LLC</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>Derek Ba***r</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Derek Baker</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>Area President</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr"/>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>dbaker@mihomes.com</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
         <is>
           <t>ADD</t>
         </is>
       </c>
-      <c r="F35" s="4" t="inlineStr">
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t>president in corridor</t>
         </is>
@@ -1755,64 +1795,64 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>Guild Mortgage Company LLC</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>Chad Overhauser</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>Divisional VP (Apollo: SVP)</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="D43" s="4" t="inlineStr">
         <is>
           <t>coverhauser@guildmortgage.net</t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr">
+      <c r="E43" s="4" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
-      <c r="F43" s="3" t="inlineStr">
+      <c r="F43" s="4" t="inlineStr">
         <is>
           <t>VP</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="inlineStr">
+      <c r="A44" s="4" t="inlineStr">
         <is>
           <t>Guild Mortgage Company LLC</t>
         </is>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>Eric Weiss</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>RVP (Apollo: SVP)</t>
         </is>
       </c>
-      <c r="D44" s="3" t="inlineStr">
+      <c r="D44" s="4" t="inlineStr">
         <is>
           <t>eweiss@guildmortgage.net</t>
         </is>
       </c>
-      <c r="E44" s="3" t="inlineStr">
+      <c r="E44" s="4" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
-      <c r="F44" s="3" t="inlineStr">
+      <c r="F44" s="4" t="inlineStr">
         <is>
           <t>VP</t>
         </is>
@@ -1834,7 +1874,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1857,7 +1897,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>only IT/security/ops VPs in corridor - no relevant POC</t>
+          <t>only IT/security/ops VPs in corridor - right seniority, wrong function</t>
         </is>
       </c>
     </row>
@@ -1881,7 +1921,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>only engineering VPs in corridor - no relevant POC</t>
+          <t>only engineering VPs in corridor</t>
         </is>
       </c>
     </row>
@@ -1941,7 +1981,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>only an Associate Director of Strategic Ops - weak</t>
+          <t>only an Associate Director of Strategic Ops</t>
         </is>
       </c>
     </row>
@@ -1965,7 +2005,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>nobody in corridor at this domain</t>
+          <t>nobody in the corridor at this domain</t>
         </is>
       </c>
     </row>
@@ -1984,7 +2024,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2007,7 +2047,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Confirmed - fits your rules, keep as-is</t>
+          <t>Confirmed - already in your data and fits the rules</t>
         </is>
       </c>
     </row>
@@ -2019,7 +2059,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Added by me - correct title found in Apollo, email still needed</t>
+          <t>Added by me - all verified emails</t>
         </is>
       </c>
     </row>
@@ -2031,7 +2071,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Not the best POC - see Reason column</t>
+          <t>Not the best POC - see Reason</t>
         </is>
       </c>
     </row>
